--- a/Team-Data/2007-08/3-28-2007-08.xlsx
+++ b/Team-Data/2007-08/3-28-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>0.444</v>
+        <v>0.437</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -682,7 +749,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L2" t="n">
         <v>4.5</v>
@@ -691,16 +758,16 @@
         <v>12.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O2" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R2" t="n">
         <v>12.3</v>
@@ -709,7 +776,7 @@
         <v>29.9</v>
       </c>
       <c r="T2" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U2" t="n">
         <v>21.6</v>
@@ -724,37 +791,37 @@
         <v>5.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -769,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
@@ -781,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -790,28 +857,28 @@
         <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.792</v>
+        <v>0.789</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
         <v>76.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O3" t="n">
         <v>20.6</v>
@@ -882,46 +949,46 @@
         <v>26.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T3" t="n">
         <v>41.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X3" t="n">
         <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA3" t="n">
         <v>22.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>100.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,13 +1003,13 @@
         <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
         <v>10</v>
@@ -951,16 +1018,16 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
@@ -969,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -984,13 +1051,13 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -1025,22 +1092,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.375</v>
+        <v>0.366</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
         <v>79.8</v>
@@ -1049,13 +1116,13 @@
         <v>0.447</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
         <v>17.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O4" t="n">
         <v>18.2</v>
@@ -1064,25 +1131,25 @@
         <v>25.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.711</v>
+        <v>0.71</v>
       </c>
       <c r="R4" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S4" t="n">
         <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U4" t="n">
         <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X4" t="n">
         <v>4.9</v>
@@ -1091,7 +1158,7 @@
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
@@ -1100,10 +1167,10 @@
         <v>96</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1118,7 +1185,7 @@
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>20</v>
@@ -1145,7 +1212,7 @@
         <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
         <v>22</v>
@@ -1154,16 +1221,16 @@
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
         <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>0.389</v>
+        <v>0.394</v>
       </c>
       <c r="H5" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
         <v>36.3</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.43</v>
@@ -1237,7 +1304,7 @@
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
         <v>18.6</v>
@@ -1246,19 +1313,19 @@
         <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R5" t="n">
         <v>13.4</v>
       </c>
       <c r="S5" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V5" t="n">
         <v>14.5</v>
@@ -1270,28 +1337,28 @@
         <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA5" t="n">
         <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC5" t="n">
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1300,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1315,10 +1382,10 @@
         <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
@@ -1339,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>11</v>
@@ -1348,7 +1415,7 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
         <v>21</v>
@@ -1357,7 +1424,7 @@
         <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,13 +1546,13 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
         <v>22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1509,13 +1576,13 @@
         <v>28</v>
       </c>
       <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="n">
         <v>3</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
       </c>
       <c r="AU6" t="n">
         <v>25</v>
@@ -1539,7 +1606,7 @@
         <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
@@ -1673,13 +1740,13 @@
         <v>8</v>
       </c>
       <c r="AL7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN7" t="n">
         <v>20</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1688,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR7" t="n">
         <v>21</v>
@@ -1721,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1852,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
@@ -2046,7 +2113,7 @@
         <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
@@ -2055,13 +2122,13 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
@@ -2225,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -2240,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>4</v>
       </c>
       <c r="AG11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>14</v>
@@ -2404,7 +2471,7 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
         <v>26</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR11" t="n">
         <v>8</v>
@@ -2428,13 +2495,13 @@
         <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>6</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" t="n">
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.411</v>
+        <v>0.403</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.443</v>
@@ -2511,40 +2578,40 @@
         <v>24.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
         <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z12" t="n">
         <v>23.6</v>
@@ -2553,13 +2620,13 @@
         <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>104</v>
+        <v>103.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>0.292</v>
+        <v>0.296</v>
       </c>
       <c r="H13" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I13" t="n">
         <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>4.2</v>
@@ -2693,25 +2760,25 @@
         <v>13.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P13" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R13" t="n">
         <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T13" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U13" t="n">
         <v>21</v>
@@ -2720,28 +2787,28 @@
         <v>14.3</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z13" t="n">
         <v>21.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2759,7 +2826,7 @@
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -2777,22 +2844,22 @@
         <v>6</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
         <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2801,16 +2868,16 @@
         <v>20</v>
       </c>
       <c r="AX13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY13" t="n">
         <v>17</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,76 +2930,76 @@
         <v>39.6</v>
       </c>
       <c r="J14" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>7.8</v>
       </c>
       <c r="M14" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S14" t="n">
         <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="V14" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W14" t="n">
         <v>8.1</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB14" t="n">
         <v>108.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="n">
         <v>4</v>
       </c>
-      <c r="AF14" t="n">
-        <v>6</v>
-      </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
@@ -2944,28 +3011,28 @@
         <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.264</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M15" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O15" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.732</v>
+        <v>0.729</v>
       </c>
       <c r="R15" t="n">
         <v>10.4</v>
       </c>
       <c r="S15" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T15" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U15" t="n">
         <v>19.1</v>
@@ -3099,28 +3166,28 @@
         <v>22.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
         <v>10</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>10</v>
@@ -3129,28 +3196,28 @@
         <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>16</v>
@@ -3162,22 +3229,22 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>19</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>0.338</v>
+        <v>0.343</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,40 +3476,40 @@
         <v>36.4</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0.735</v>
       </c>
       <c r="R17" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="S17" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U17" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
         <v>14.5</v>
@@ -3460,16 +3527,16 @@
         <v>21.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3484,13 +3551,13 @@
         <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>15</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3517,16 +3584,16 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
         <v>21</v>
@@ -3538,7 +3605,7 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -3573,22 +3640,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>0.254</v>
+        <v>0.257</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J18" t="n">
         <v>82.59999999999999</v>
@@ -3603,13 +3670,13 @@
         <v>15.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O18" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.733</v>
@@ -3618,16 +3685,16 @@
         <v>11.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
         <v>19.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W18" t="n">
         <v>7.6</v>
@@ -3636,7 +3703,7 @@
         <v>3.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z18" t="n">
         <v>23.1</v>
@@ -3645,28 +3712,28 @@
         <v>17.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.5</v>
+        <v>94.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AD18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE18" t="n">
         <v>27</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>27</v>
       </c>
       <c r="AG18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH18" t="n">
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>9</v>
@@ -3693,13 +3760,13 @@
         <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
@@ -3708,13 +3775,13 @@
         <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -3755,34 +3822,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
         <v>31</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.425</v>
+        <v>0.431</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J19" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="K19" t="n">
         <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M19" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
         <v>0.349</v>
@@ -3794,16 +3861,16 @@
         <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T19" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
@@ -3812,10 +3879,10 @@
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
         <v>4.4</v>
@@ -3827,16 +3894,16 @@
         <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
@@ -3845,19 +3912,19 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
@@ -3869,10 +3936,10 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -3887,13 +3954,13 @@
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -3905,7 +3972,7 @@
         <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" t="n">
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,7 +4022,7 @@
         <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.463</v>
@@ -3973,28 +4040,28 @@
         <v>15.9</v>
       </c>
       <c r="P20" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.773</v>
       </c>
       <c r="R20" t="n">
         <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T20" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X20" t="n">
         <v>3.9</v>
@@ -4009,19 +4076,19 @@
         <v>19.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
         <v>3</v>
@@ -4033,19 +4100,19 @@
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM20" t="n">
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4054,19 +4121,19 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
         <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>0.278</v>
+        <v>0.282</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
         <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
@@ -4149,19 +4216,19 @@
         <v>17.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="O21" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R21" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
@@ -4173,7 +4240,7 @@
         <v>18.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W21" t="n">
         <v>6.3</v>
@@ -4188,7 +4255,7 @@
         <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB21" t="n">
         <v>95.5</v>
@@ -4197,7 +4264,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4230,16 +4297,16 @@
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
@@ -4251,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
         <v>26</v>
@@ -4269,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J22" t="n">
         <v>78.5</v>
@@ -4328,7 +4395,7 @@
         <v>9.6</v>
       </c>
       <c r="M22" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="N22" t="n">
         <v>0.386</v>
@@ -4340,13 +4407,13 @@
         <v>28.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R22" t="n">
         <v>9.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T22" t="n">
         <v>42.1</v>
@@ -4364,10 +4431,10 @@
         <v>4.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA22" t="n">
         <v>23.5</v>
@@ -4376,7 +4443,7 @@
         <v>104.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4421,13 +4488,13 @@
         <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4436,16 +4503,16 @@
         <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>3</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
         <v>37</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,10 +4568,10 @@
         <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
@@ -4513,25 +4580,25 @@
         <v>11.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="O23" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P23" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q23" t="n">
         <v>0.705</v>
       </c>
       <c r="R23" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S23" t="n">
         <v>29</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U23" t="n">
         <v>20.3</v>
@@ -4540,37 +4607,37 @@
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z23" t="n">
         <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB23" t="n">
         <v>96.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG23" t="n">
         <v>16</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>17</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
@@ -4582,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4603,13 +4670,13 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
         <v>23</v>
@@ -4624,7 +4691,7 @@
         <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
@@ -4633,7 +4700,7 @@
         <v>15</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4686,19 +4753,19 @@
         <v>82.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0.499</v>
       </c>
       <c r="L24" t="n">
         <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
         <v>0.391</v>
       </c>
       <c r="O24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P24" t="n">
         <v>23.6</v>
@@ -4710,13 +4777,13 @@
         <v>8.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T24" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U24" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="V24" t="n">
         <v>14.5</v>
@@ -4728,40 +4795,40 @@
         <v>6.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.9</v>
+        <v>110</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG24" t="n">
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4773,16 +4840,16 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP24" t="n">
         <v>23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4797,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4812,7 +4879,7 @@
         <v>8</v>
       </c>
       <c r="BA24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4940,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>23</v>
@@ -4964,13 +5031,13 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT25" t="n">
         <v>26</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
         <v>32</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>0.444</v>
+        <v>0.451</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5059,22 +5126,22 @@
         <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O26" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0.796</v>
       </c>
       <c r="R26" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S26" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T26" t="n">
         <v>40.4</v>
@@ -5083,10 +5150,10 @@
         <v>19.1</v>
       </c>
       <c r="V26" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W26" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.2</v>
@@ -5095,19 +5162,19 @@
         <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5128,13 +5195,13 @@
         <v>19</v>
       </c>
       <c r="AK26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>17</v>
       </c>
       <c r="AM26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="n">
         <v>12</v>
@@ -5143,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
@@ -5229,28 +5296,28 @@
         <v>35.7</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L27" t="n">
         <v>7.5</v>
       </c>
       <c r="M27" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O27" t="n">
         <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R27" t="n">
         <v>9.699999999999999</v>
@@ -5265,7 +5332,7 @@
         <v>21.1</v>
       </c>
       <c r="V27" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5277,19 +5344,19 @@
         <v>4.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA27" t="n">
         <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -5301,19 +5368,19 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
       </c>
       <c r="AL27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM27" t="n">
         <v>8</v>
@@ -5337,7 +5404,7 @@
         <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>17</v>
@@ -5346,10 +5413,10 @@
         <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
@@ -5364,7 +5431,7 @@
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" t="n">
-        <v>0.233</v>
+        <v>0.236</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5423,25 +5490,25 @@
         <v>11.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P28" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="n">
         <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S28" t="n">
         <v>32.7</v>
       </c>
       <c r="T28" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U28" t="n">
         <v>21.4</v>
@@ -5456,7 +5523,7 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z28" t="n">
         <v>20.6</v>
@@ -5468,10 +5535,10 @@
         <v>97.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>-8.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5519,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="n">
         <v>15</v>
@@ -5543,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" t="n">
         <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H29" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I29" t="n">
         <v>38.2</v>
       </c>
       <c r="J29" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.467</v>
@@ -5602,28 +5669,28 @@
         <v>7.2</v>
       </c>
       <c r="M29" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="O29" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P29" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.6</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
         <v>23.4</v>
@@ -5638,31 +5705,31 @@
         <v>4.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB29" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF29" t="n">
         <v>15</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
         <v>10</v>
@@ -5671,10 +5738,10 @@
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5692,13 +5759,13 @@
         <v>30</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
         <v>26</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5719,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -5757,40 +5824,40 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F30" t="n">
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.658</v>
+        <v>0.653</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="L30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M30" t="n">
         <v>12.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O30" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="P30" t="n">
         <v>29</v>
@@ -5799,7 +5866,7 @@
         <v>0.757</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S30" t="n">
         <v>29.3</v>
@@ -5811,31 +5878,31 @@
         <v>26.3</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z30" t="n">
         <v>24.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.7</v>
+        <v>106.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5898,7 +5965,7 @@
         <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F31" t="n">
         <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0.528</v>
+        <v>0.521</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L31" t="n">
         <v>6.7</v>
@@ -5969,13 +6036,13 @@
         <v>19.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O31" t="n">
         <v>19.1</v>
       </c>
       <c r="P31" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q31" t="n">
         <v>0.787</v>
@@ -5993,7 +6060,7 @@
         <v>19.3</v>
       </c>
       <c r="V31" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W31" t="n">
         <v>7.8</v>
@@ -6011,16 +6078,16 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
         <v>14</v>
@@ -6032,10 +6099,10 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-28-2007-08</t>
+          <t>2008-03-28</t>
         </is>
       </c>
     </row>
